--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22417,7 +22435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22461,6 +22479,35 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1977_78_0076 'TJ Sokol Ostrava-Poruba' prev→CLUB_S1976_77_0502 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0014</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1977_78_0014 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1977_78_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -26800,8 +26847,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -26881,7 +26926,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -34410,10 +34454,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -38508,7 +38548,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
@@ -42445,7 +42484,6 @@
         </is>
       </c>
     </row>
-    <row r="278"/>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
@@ -43949,7 +43987,6 @@
         </is>
       </c>
     </row>
-    <row r="313"/>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
@@ -47709,7 +47746,6 @@
         </is>
       </c>
     </row>
-    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -50503,7 +50539,6 @@
         </is>
       </c>
     </row>
-    <row r="461"/>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
@@ -52464,7 +52499,6 @@
         </is>
       </c>
     </row>
-    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
@@ -54001,6 +54035,105 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0076</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0076 'TJ Sokol Ostrava-Poruba' prev→CLUB_S1976_77_0502 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0014</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1977_78_0014 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1977_78_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22435,7 +22435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22485,7 +22485,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1977_78_0076 'TJ Sokol Ostrava-Poruba' prev→CLUB_S1976_77_0502 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22495,17 +22495,576 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1977_78_0014</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1977_78_0014 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1977_78_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAO Zábřeh' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -26847,6 +27406,8 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -26877,6 +27438,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0001</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -26889,6 +27455,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0003</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -26901,6 +27472,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0003</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -26913,6 +27489,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0009</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -26926,6 +27507,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -30439,7 +31021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J527"/>
+  <dimension ref="A1:J533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -30740,12 +31322,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -31217,12 +31799,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -31474,12 +32056,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -31600,12 +32182,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -31726,12 +32308,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -32292,12 +32874,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32732,12 +33314,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32774,12 +33356,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -32957,12 +33539,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -32999,12 +33581,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -33397,12 +33979,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -34454,6 +35036,10 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -35184,12 +35770,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -36724,12 +37310,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -38502,12 +39088,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -38548,6 +39134,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
@@ -38628,12 +39215,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38806,12 +39393,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -39283,12 +39870,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -39555,12 +40142,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -39879,12 +40466,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -39973,12 +40560,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40020,12 +40607,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -41447,12 +42034,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -42484,6 +43071,7 @@
         </is>
       </c>
     </row>
+    <row r="278"/>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
@@ -42522,12 +43110,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -42569,12 +43157,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -43987,6 +44575,7 @@
         </is>
       </c>
     </row>
+    <row r="313"/>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
@@ -44282,12 +44871,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -46550,12 +47139,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice.</t>
+          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice. || TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>SSM SNV Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -47569,12 +48158,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno.</t>
+          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno. || TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Blešno</t>
+          <t>Moravská Třebová</t>
         </is>
       </c>
     </row>
@@ -47737,15 +48326,16 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno.</t>
+          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno. || TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Blešno</t>
-        </is>
-      </c>
-    </row>
+          <t>Moravská Třebová</t>
+        </is>
+      </c>
+    </row>
+    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -47784,12 +48374,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -47920,12 +48510,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -48261,12 +48851,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Zábřeh = TJ Slovan Zábřeh (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). VTJ Dukla Zábřeh = vojensky. POZOR: NE Zabreh u Ostravy (mestska cast). city Zábřeh.</t>
+          <t>Zábřeh = TJ Slovan Zábřeh (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). VTJ Dukla Zábřeh = vojensky. POZOR: NE Zabreh u Ostravy (mestska cast). city Zábřeh. || TBD: city 'ČSAO Zábřeh' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>ČSAO Zábřeh</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -49771,12 +50361,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -50539,6 +51129,7 @@
         </is>
       </c>
     </row>
+    <row r="461"/>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
@@ -50661,12 +51252,12 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -50787,12 +51378,12 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek. || TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>VP Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -51133,12 +51724,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -52499,6 +53090,7 @@
         </is>
       </c>
     </row>
+    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
@@ -52658,12 +53250,12 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom.</t>
+          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom. || TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Družstevník Krizovany nad Dudváhom</t>
+          <t>Krizovany nad Dudváhom</t>
         </is>
       </c>
     </row>
@@ -53321,6 +53913,198 @@
       <c r="J527" t="inlineStr">
         <is>
           <t>JIP Větřní</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0188</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0277</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0312</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0395</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0461</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0507</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54045,11 +54829,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -54094,21 +54878,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0076</t>
+          <t>CLUB_S1977_78_0006</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0076 'TJ Sokol Ostrava-Poruba' prev→CLUB_S1976_77_0502 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -54116,24 +54898,962 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1977_78_0014</t>
+          <t>CLUB_S1977_78_0017</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1977_78_0014 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1977_78_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0023</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0029</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0042</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0052</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0053</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0057</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0058</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0067</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0076</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0112</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0147</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0186</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0190</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0194</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0205</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0205</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0211</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0218</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0220</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0221</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0228</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0252</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0278</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0279</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0319</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0352</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0368</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0382</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0390</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0392</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0394</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0396</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0399</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0407</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ČSAO Zábřeh' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0422</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0443</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0464</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0467</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0475</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0511</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0188</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0277</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0312</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0395</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0461</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1977_78_0507</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22435,7 +22435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22485,7 +22485,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22497,7 +22497,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22509,7 +22509,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22521,7 +22521,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22533,7 +22533,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22545,7 +22545,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22557,7 +22557,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22569,7 +22569,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22581,7 +22581,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22593,7 +22593,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22605,7 +22605,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22617,7 +22617,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22629,7 +22629,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22641,7 +22641,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22677,7 +22677,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22689,7 +22689,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -22701,7 +22701,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22713,7 +22713,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22725,7 +22725,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -22737,7 +22737,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22749,7 +22749,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22761,7 +22761,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22773,7 +22773,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22785,7 +22785,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22797,7 +22797,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22809,7 +22809,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -22833,7 +22833,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22845,7 +22845,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22857,7 +22857,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22869,7 +22869,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22881,7 +22881,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22893,7 +22893,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22905,7 +22905,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22917,7 +22917,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAO Zábřeh' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22929,142 +22929,10 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23081,7 +22949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23140,6 +23008,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23182,6 +23055,11 @@
           <t>12 týmů + baráž (11. vs 12.). Mistr: Poldi SONP Kladno.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23229,6 +23107,11 @@
           <t>Série Gottwaldov - Zvolen 4:2. 1., 2. a 5. utkání doma; případné 7. utkání v Ostravě.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23271,6 +23154,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK). Kvalifikace o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23313,6 +23201,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23355,6 +23248,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23397,6 +23295,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23439,6 +23342,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23481,6 +23389,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23523,6 +23436,11 @@
           <t>II.ČNHL: 3 skupiny po 8. Nově založená soutěž.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23565,6 +23483,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23607,6 +23530,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23649,6 +23577,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23958,6 +23891,11 @@
           <t>Česká kvalifikace o 2. ČNHL ve 4 dvojzápasových sériích.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0023</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24042,6 +23980,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24168,6 +24111,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0028</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24210,6 +24158,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0029</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24252,6 +24205,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0030</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -24294,6 +24252,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0031</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24336,6 +24299,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0032</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24378,6 +24346,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0033</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -24420,6 +24393,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0034</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -24462,6 +24440,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0035</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -24504,6 +24487,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -24546,6 +24534,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0037</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -24640,6 +24633,11 @@
           <t>kvalifikace o II.třídu (přeborníci okresů)</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0039</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -24850,6 +24848,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0044</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -24892,6 +24895,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0045</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25060,6 +25068,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0046</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25102,6 +25115,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0047</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25144,6 +25162,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25191,6 +25214,11 @@
           <t>o postup do KP</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -25280,6 +25308,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -25322,6 +25355,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -25364,6 +25402,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25406,6 +25449,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0054</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25448,6 +25496,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0055</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25490,6 +25543,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0056</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25537,6 +25595,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0057</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -25579,6 +25642,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0058</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25621,6 +25689,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0059</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -25789,6 +25862,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0060</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -25831,6 +25909,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0061</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -25873,6 +25956,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0062</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -25915,6 +26003,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0063</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -25999,6 +26092,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0064</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26041,6 +26139,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0065</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26214,6 +26317,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0076</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26256,6 +26364,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0077</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26298,6 +26411,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0078</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -26723,6 +26841,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0088</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -26765,6 +26888,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0089</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26807,6 +26935,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0090</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -26933,6 +27066,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0093</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27153,6 +27291,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0098</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -27193,6 +27336,11 @@
       <c r="J96" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0099</t>
         </is>
       </c>
     </row>
@@ -31322,12 +31470,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32056,12 +32204,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -32308,12 +32456,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -33539,12 +33687,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -33581,12 +33729,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -39870,12 +40018,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -48158,12 +48306,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno. || TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno.</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Moravská Třebová</t>
+          <t>Blešno</t>
         </is>
       </c>
     </row>
@@ -48326,12 +48474,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno. || TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Blešno = TJ Sokol Blešno (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). city Blešno.</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Moravská Třebová</t>
+          <t>Blešno</t>
         </is>
       </c>
     </row>
@@ -48510,12 +48658,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -48851,12 +48999,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Zábřeh = TJ Slovan Zábřeh (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). VTJ Dukla Zábřeh = vojensky. POZOR: NE Zabreh u Ostravy (mestska cast). city Zábřeh. || TBD: city 'ČSAO Zábřeh' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Zábřeh = TJ Slovan Zábřeh (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). VTJ Dukla Zábřeh = vojensky. POZOR: NE Zabreh u Ostravy (mestska cast). city Zábřeh.</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou</t>
+          <t>Zábřeh</t>
         </is>
       </c>
     </row>
@@ -51252,12 +51400,12 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -54829,7 +54977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -54883,12 +55031,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0006</t>
+          <t>CLUB_S1977_78_0017</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54903,12 +55051,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0017</t>
+          <t>CLUB_S1977_78_0026</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54923,12 +55071,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0023</t>
+          <t>CLUB_S1977_78_0042</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54943,12 +55091,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0026</t>
+          <t>CLUB_S1977_78_0052</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54963,12 +55111,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0029</t>
+          <t>CLUB_S1977_78_0053</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54983,12 +55131,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0042</t>
+          <t>CLUB_S1977_78_0067</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55003,12 +55151,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0052</t>
+          <t>CLUB_S1977_78_0076</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55023,12 +55171,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0053</t>
+          <t>CLUB_S1977_78_0112</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55043,12 +55191,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0057</t>
+          <t>CLUB_S1977_78_0147</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55063,12 +55211,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0058</t>
+          <t>CLUB_S1977_78_0186</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55083,12 +55231,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0067</t>
+          <t>CLUB_S1977_78_0190</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55103,12 +55251,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0076</t>
+          <t>CLUB_S1977_78_0194</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55123,12 +55271,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0112</t>
+          <t>CLUB_S1977_78_0205</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55143,12 +55291,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0147</t>
+          <t>CLUB_S1977_78_0211</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55163,12 +55311,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0186</t>
+          <t>CLUB_S1977_78_0218</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55183,7 +55331,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0190</t>
+          <t>CLUB_S1977_78_0220</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -55203,12 +55351,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0194</t>
+          <t>CLUB_S1977_78_0221</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55223,12 +55371,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0205</t>
+          <t>CLUB_S1977_78_0228</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -55243,12 +55391,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0205</t>
+          <t>CLUB_S1977_78_0252</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55263,12 +55411,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0211</t>
+          <t>CLUB_S1977_78_0278</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55283,12 +55431,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0218</t>
+          <t>CLUB_S1977_78_0279</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55303,12 +55451,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0220</t>
+          <t>CLUB_S1977_78_0319</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55323,12 +55471,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0221</t>
+          <t>CLUB_S1977_78_0352</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -55343,12 +55491,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0228</t>
+          <t>CLUB_S1977_78_0368</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55363,12 +55511,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0252</t>
+          <t>CLUB_S1977_78_0382</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -55383,12 +55531,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0278</t>
+          <t>CLUB_S1977_78_0392</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -55403,12 +55551,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0279</t>
+          <t>CLUB_S1977_78_0396</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55423,12 +55571,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0319</t>
+          <t>CLUB_S1977_78_0422</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -55443,12 +55591,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0352</t>
+          <t>CLUB_S1977_78_0443</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55463,12 +55611,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0368</t>
+          <t>CLUB_S1977_78_0467</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55483,12 +55631,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0382</t>
+          <t>CLUB_S1977_78_0475</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55503,12 +55651,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0390</t>
+          <t>CLUB_S1977_78_0511</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55523,12 +55671,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0392</t>
+          <t>CLUB_S1977_78_0188</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55543,12 +55691,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0394</t>
+          <t>CLUB_S1977_78_0277</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Blešno' → 'Moravská Třebová' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55563,12 +55711,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0396</t>
+          <t>CLUB_S1977_78_0312</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55583,12 +55731,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0399</t>
+          <t>CLUB_S1977_78_0395</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55603,12 +55751,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0407</t>
+          <t>CLUB_S1977_78_0461</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ČSAO Zábřeh' → 'Veselí nad Moravou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55623,237 +55771,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1977_78_0422</t>
+          <t>CLUB_S1977_78_0507</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0443</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0464</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0467</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0475</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0511</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0188</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0277</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0312</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0395</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0461</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1977_78_0507</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -21064,7 +21064,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / TJ Slovan Levice nenastoupil k prvnímu utkání a následně odstoupil ze soutěže</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
@@ -22435,7 +22435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22483,21 +22483,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30ZASL</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] TJ Slovan Levice nenastoupil k prvnímu utkání a následně odstoupil ze soutěže</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22509,7 +22514,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22521,7 +22526,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22533,7 +22538,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22545,7 +22550,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22557,7 +22562,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22569,7 +22574,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1976_77_0502 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22581,7 +22586,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22605,7 +22610,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22617,7 +22622,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22629,7 +22634,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22641,7 +22646,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22653,7 +22658,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22689,7 +22694,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -22701,7 +22706,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22713,7 +22718,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22725,7 +22730,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -22737,7 +22742,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22749,7 +22754,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22761,7 +22766,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22773,7 +22778,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22785,7 +22790,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22797,7 +22802,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22809,7 +22814,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22821,7 +22826,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -22833,7 +22838,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22845,7 +22850,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22857,7 +22862,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22869,7 +22874,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22933,6 +22938,18 @@
         </is>
       </c>
       <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -59751,7 +59751,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M16" t="n">
         <v>24</v>
@@ -60583,7 +60583,7 @@
         <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M17" t="n">
         <v>21</v>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -35201,10 +35201,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -39299,7 +39295,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
@@ -43236,7 +43231,6 @@
         </is>
       </c>
     </row>
-    <row r="278"/>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
@@ -44740,7 +44734,6 @@
         </is>
       </c>
     </row>
-    <row r="313"/>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
@@ -48500,7 +48493,6 @@
         </is>
       </c>
     </row>
-    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -51294,7 +51286,6 @@
         </is>
       </c>
     </row>
-    <row r="461"/>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
@@ -53255,7 +53246,6 @@
         </is>
       </c>
     </row>
-    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -22966,7 +22966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23030,6 +23030,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27571,8 +27581,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -27672,7 +27680,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -23312,6 +23312,16 @@
           <t>NODE_S1977_78_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23326,6 +23336,14 @@
         <is>
           <t>NODE_S1976_77_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23359,6 +23377,8 @@
           <t>NODE_S1977_78_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23373,6 +23393,14 @@
         <is>
           <t>NODE_S1976_77_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -23406,6 +23434,8 @@
           <t>NODE_S1977_78_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23420,6 +23450,14 @@
         <is>
           <t>NODE_S1976_77_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -23856,6 +23894,8 @@
           <t>NODE_S1977_78_0015</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23870,6 +23910,14 @@
         <is>
           <t>Topoľčany - Prešov 3:0; 1. a 3. utkání doma.</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -24316,6 +24364,8 @@
           <t>NODE_S1977_78_0024</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24330,6 +24380,14 @@
         <is>
           <t>NODE_S1976_77_0032</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -24959,6 +25017,12 @@
           <t>NODE_S1977_78_0040</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0044</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24968,6 +25032,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -25043,6 +25115,8 @@
           <t>NODE_S1977_78_0040</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25052,6 +25126,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -25753,6 +25835,16 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0060</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0061</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25762,6 +25854,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -25795,6 +25895,8 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25804,6 +25906,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -25837,6 +25947,8 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25846,6 +25958,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>5.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -26067,6 +26187,8 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26076,6 +26198,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -26475,6 +26605,12 @@
           <t>NODE_S1977_78_0073</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0078</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26484,6 +26620,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -26517,6 +26661,12 @@
           <t>NODE_S1977_78_0073</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0078</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26526,6 +26676,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -26601,6 +26759,8 @@
           <t>NODE_S1977_78_0073</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26610,6 +26770,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1.–6. ZČ</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -27125,11 +27293,8 @@
           <t>REG_SVM</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NODE_S1977_78_0021</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27144,6 +27309,14 @@
         <is>
           <t>finále o postup do KP I.třídy</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -27486,6 +27659,16 @@
           <t>NODE_S1977_78_0094</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0099</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0100</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27495,6 +27678,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -27528,6 +27719,8 @@
           <t>NODE_S1977_78_0094</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27537,6 +27730,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -27570,6 +27771,8 @@
           <t>NODE_S1977_78_0094</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27580,7 +27783,17 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -27680,6 +27893,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -720,6 +720,11 @@
           <t>Poldi SONP Kladno</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -23377,8 +23382,6 @@
           <t>NODE_S1977_78_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23434,8 +23437,6 @@
           <t>NODE_S1977_78_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23894,8 +23895,6 @@
           <t>NODE_S1977_78_0015</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24364,8 +24363,6 @@
           <t>NODE_S1977_78_0024</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25017,7 +25014,6 @@
           <t>NODE_S1977_78_0040</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>NODE_S1977_78_0044</t>
@@ -25115,8 +25111,6 @@
           <t>NODE_S1977_78_0040</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25895,8 +25889,6 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25947,8 +25939,6 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26187,8 +26177,6 @@
           <t>NODE_S1977_78_0057</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26605,7 +26593,6 @@
           <t>NODE_S1977_78_0073</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>NODE_S1977_78_0078</t>
@@ -26661,7 +26648,6 @@
           <t>NODE_S1977_78_0073</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>NODE_S1977_78_0078</t>
@@ -26759,8 +26745,6 @@
           <t>NODE_S1977_78_0073</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27293,8 +27277,6 @@
           <t>REG_SVM</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27719,8 +27701,6 @@
           <t>NODE_S1977_78_0094</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27771,8 +27751,6 @@
           <t>NODE_S1977_78_0094</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27792,8 +27770,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -27893,7 +27869,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -54495,7 +54470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55191,6 +55166,18 @@
       <c r="B58" t="inlineStr">
         <is>
           <t>PDF nese finále SVK divize a vítěze slovenských KP; prepared/výstup měly rozpadlé KVAL a falešné finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Poldi SONP Kladno</t>
         </is>
       </c>
     </row>

--- a/data/S1977_78_FINAL.xlsx
+++ b/data/S1977_78_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22440,7 +22440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22955,6 +22955,23 @@
         </is>
       </c>
       <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0090</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: '30_Severomoravský finále o postup do KP I.třídy'</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27770,6 +27787,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -27869,6 +27888,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -35397,6 +35417,10 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -39491,6 +39515,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
@@ -43427,6 +43452,7 @@
         </is>
       </c>
     </row>
+    <row r="278"/>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
@@ -44930,6 +44956,7 @@
         </is>
       </c>
     </row>
+    <row r="313"/>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
@@ -48689,6 +48716,7 @@
         </is>
       </c>
     </row>
+    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -51482,6 +51510,7 @@
         </is>
       </c>
     </row>
+    <row r="461"/>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
@@ -53442,6 +53471,7 @@
         </is>
       </c>
     </row>
+    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
@@ -55192,7 +55222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -55995,8 +56025,28 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0090</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: '30_Severomoravský finále o postup do KP I.třídy'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
